--- a/assets/downloads/CotizacionVICTOR LUIS SAN MIGUEL CASAS.xlsx
+++ b/assets/downloads/CotizacionVICTOR LUIS SAN MIGUEL CASAS.xlsx
@@ -4,21 +4,21 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
     <sheet name="2" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$103</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -53,7 +53,7 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>0 Kg</t>
+    <t>200 Kg</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
@@ -113,9 +113,9 @@
     <t>Hola VICTOR LUIS SAN MIGUEL CASAS 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $0
-        ☑️Impuestos: $580.8
-        ☑️ Total: $580.8
+        ☑️Costo CBM: $415.8
+        ☑️Impuestos: $452.17
+        ☑️ Total: $867.97
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -174,34 +174,25 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>GUANTES LARGOS TACTICOS</t>
-  </si>
-  <si>
-    <t>GUANTES CORTOS TACTICOS</t>
-  </si>
-  <si>
-    <t>MOCHILA TACTICA</t>
-  </si>
-  <si>
-    <t>MOCHILA PARA SENDERISMO</t>
-  </si>
-  <si>
-    <t>MOCHILA TACTICA MULTIBOLSILLOS</t>
-  </si>
-  <si>
-    <t>MORRAL TÁCTICO</t>
-  </si>
-  <si>
-    <t>CORREA TÁCTICA</t>
-  </si>
-  <si>
-    <t>MASCARA TACTICA</t>
-  </si>
-  <si>
-    <t>PACK RODILLERAS Y CODERAS TACTICAS</t>
-  </si>
-  <si>
-    <t>PASAMONTAÑAS TACTICA</t>
+    <t>MOCHILA DE HIDRATACION</t>
+  </si>
+  <si>
+    <t>MOCHILA TACTICA MILITAR</t>
+  </si>
+  <si>
+    <t>LONCHERA TACTICA MILITAR</t>
+  </si>
+  <si>
+    <t>PASAMONTAÑA MILITAR</t>
+  </si>
+  <si>
+    <t>GUANTES MILITAR</t>
+  </si>
+  <si>
+    <t>GUANTES CORTOS MILITAR</t>
+  </si>
+  <si>
+    <t>MAQUINA DE SUBLIMACION DE TRANSFERENCIA</t>
   </si>
   <si>
     <r>
@@ -1217,7 +1208,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1209675" cy="1190625"/>
@@ -1247,7 +1238,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4057650" cy="3429000"/>
@@ -1566,7 +1557,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="10.77734375" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" style="1"/>
@@ -1716,7 +1707,9 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="16">
+        <v>10741433066</v>
+      </c>
       <c r="D10" s="34"/>
       <c r="E10" s="27" t="s">
         <v>13</v>
@@ -1737,7 +1730,9 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="17">
+        <v>51956686057</v>
+      </c>
       <c r="D11" s="35"/>
       <c r="E11" s="24" t="s">
         <v>17</v>
@@ -1751,7 +1746,7 @@
         <v>19</v>
       </c>
       <c r="J11" s="95" t="str">
-        <f>'2'!M7</f>
+        <f>'2'!J7</f>
         <v>0</v>
       </c>
       <c r="K11" s="73"/>
@@ -1802,7 +1797,7 @@
       <c r="I14" s="67"/>
       <c r="J14" s="67"/>
       <c r="K14" s="14" t="str">
-        <f>'2'!M11</f>
+        <f>'2'!J11</f>
         <v>0</v>
       </c>
       <c r="L14" s="9" t="s">
@@ -1822,7 +1817,7 @@
       <c r="I15" s="68"/>
       <c r="J15" s="68"/>
       <c r="K15" s="15" t="str">
-        <f>'2'!M14 + '2'!M17</f>
+        <f>'2'!J14 + '2'!J17</f>
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
@@ -1908,11 +1903,11 @@
       <c r="H20" s="49"/>
       <c r="I20" s="49"/>
       <c r="J20" s="20" t="str">
-        <f>MAX('2'!C27:L27)</f>
+        <f>MAX('2'!C27:I27)</f>
         <v>0</v>
       </c>
       <c r="K20" s="14" t="str">
-        <f>'2'!M28</f>
+        <f>'2'!J28</f>
         <v>0</v>
       </c>
       <c r="L20" s="9" t="s">
@@ -1937,7 +1932,7 @@
         <v>0.16</v>
       </c>
       <c r="K21" s="14" t="str">
-        <f>'2'!M29</f>
+        <f>'2'!J29</f>
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
@@ -1959,7 +1954,7 @@
         <v>0.02</v>
       </c>
       <c r="K22" s="14" t="str">
-        <f>'2'!M30</f>
+        <f>'2'!J30</f>
         <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
@@ -2014,7 +2009,7 @@
         <v>35</v>
       </c>
       <c r="K25" s="15" t="str">
-        <f>'2'!M31</f>
+        <f>'2'!J31</f>
         <v>0</v>
       </c>
       <c r="L25" s="12" t="s">
@@ -2102,7 +2097,7 @@
       <c r="I30" s="49"/>
       <c r="J30" s="49"/>
       <c r="K30" s="14" t="str">
-        <f>IF('2'!Q7&lt;1, '2'!Q7*J11, '2'!Q7*J11)</f>
+        <f>IF(J11&lt;1, '2'!N7, '2'!N7*J11)</f>
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
@@ -2433,150 +2428,74 @@
       <c r="L42" s="3"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="18">
-      <c r="B43" s="91">
-        <v>8</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="93" t="str">
+        <f>SUM(F36:F42)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="94" t="str">
+        <f>SUM(J36:J42)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="64"/>
+      <c r="L43" s="64"/>
+    </row>
+    <row r="44" spans="1:14" customHeight="1" ht="18">
+      <c r="B44" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5" t="str">
-        <f>'2'!J10</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="88" t="str">
-        <f>'2'!J8</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="88" t="str">
-        <f>'2'!J46</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="88" t="str">
-        <f>'2'!J44</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="89" t="str">
-        <f>'2'!J47</f>
-        <v>0</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="1:14" customHeight="1" ht="18">
-      <c r="B44" s="91">
-        <v>9</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="64"/>
+      <c r="K44" s="64"/>
+      <c r="L44" s="64"/>
+    </row>
+    <row r="45" spans="1:14" customHeight="1" ht="18">
+      <c r="B45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5" t="str">
-        <f>'2'!K10</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="88" t="str">
-        <f>'2'!K8</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="88" t="str">
-        <f>'2'!K46</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="88" t="str">
-        <f>'2'!K44</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="89" t="str">
-        <f>'2'!K47</f>
-        <v>0</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="1:14" customHeight="1" ht="18">
-      <c r="B45" s="91">
-        <v>10</v>
-      </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="64"/>
+      <c r="L45" s="64"/>
+    </row>
+    <row r="46" spans="1:14" customHeight="1" ht="18">
+      <c r="B46" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5" t="str">
-        <f>'2'!L10</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="88" t="str">
-        <f>'2'!L8</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="88" t="str">
-        <f>'2'!L46</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="88" t="str">
-        <f>'2'!L44</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="89" t="str">
-        <f>'2'!L47</f>
-        <v>0</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="1:14" customHeight="1" ht="18">
-      <c r="B46" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="92"/>
-      <c r="D46" s="92"/>
-      <c r="E46" s="92"/>
-      <c r="F46" s="93" t="str">
-        <f>SUM(F36:F45)</f>
-        <v>0</v>
-      </c>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
       <c r="G46" s="64"/>
       <c r="H46" s="64"/>
       <c r="I46" s="64"/>
-      <c r="J46" s="94" t="str">
-        <f>SUM(J36:J45)</f>
-        <v>0</v>
-      </c>
+      <c r="J46" s="64"/>
       <c r="K46" s="64"/>
       <c r="L46" s="64"/>
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="18">
-      <c r="B47" s="64" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="true"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">*</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="false"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">No se emite comprobante por concepto de "PERCEPCIÓN, ANTI DUMPING, GESTIÓN DE COMPRA"</t>
-          </r>
-        </is>
+      <c r="B47" s="64" t="s">
+        <v>59</v>
       </c>
       <c r="C47" s="64"/>
       <c r="D47" s="64"/>
@@ -2589,201 +2508,127 @@
       <c r="K47" s="64"/>
       <c r="L47" s="64"/>
     </row>
-    <row r="48" spans="1:14" customHeight="1" ht="18">
-      <c r="B48" s="64" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="true"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">*</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="false"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">A nosotros se nos pagan los </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="true"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">Gastos Logísticos + Impuestos</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="false"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve"> una semana antes de que el contenedor</t>
-          </r>
-        </is>
-      </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="64"/>
-      <c r="J48" s="64"/>
-      <c r="K48" s="64"/>
-      <c r="L48" s="64"/>
-    </row>
-    <row r="49" spans="1:14" customHeight="1" ht="18">
-      <c r="B49" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="64"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="64"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
-      <c r="I49" s="64"/>
-      <c r="J49" s="64"/>
-      <c r="K49" s="64"/>
-      <c r="L49" s="64"/>
-    </row>
-    <row r="50" spans="1:14" customHeight="1" ht="18">
-      <c r="B50" s="64" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="true"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">*</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="false"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="14"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">El tipo de cambio referencial usado para la conversión a soles es del 3.70</t>
-          </r>
-        </is>
-      </c>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="64"/>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64"/>
-      <c r="H50" s="64"/>
-      <c r="I50" s="64"/>
-      <c r="J50" s="64"/>
-      <c r="K50" s="64"/>
-      <c r="L50" s="64"/>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-    </row>
-    <row r="52" spans="1:14" customHeight="1" ht="9">
+    <row r="48" spans="1:14">
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+    </row>
+    <row r="49" spans="1:14" customHeight="1" ht="9">
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="38"/>
+      <c r="L49" s="38"/>
+      <c r="M49" s="38"/>
+    </row>
+    <row r="50" spans="1:14" customHeight="1" ht="31.8">
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="37"/>
+      <c r="M50" s="37"/>
+    </row>
+    <row r="51" spans="1:14" customHeight="1" ht="21">
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="B52" s="38"/>
       <c r="C52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-    </row>
-    <row r="53" spans="1:14" customHeight="1" ht="31.8">
+    </row>
+    <row r="53" spans="1:14">
       <c r="B53" s="38"/>
       <c r="C53" s="38"/>
-      <c r="D53" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="37"/>
-      <c r="K53" s="37"/>
-      <c r="L53" s="37"/>
-      <c r="M53" s="37"/>
     </row>
     <row r="54" spans="1:14" customHeight="1" ht="21">
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="53" t="s">
+      <c r="B54" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="B56" s="71" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="71"/>
+      <c r="L56" s="71"/>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="B57" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="E54" s="53"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="B56" s="38"/>
-      <c r="C56" s="38"/>
-    </row>
-    <row r="57" spans="1:14" customHeight="1" ht="21">
-      <c r="B57" s="70" t="s">
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="71"/>
+      <c r="L57" s="71"/>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="B58" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="70"/>
-      <c r="L57" s="70"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+      <c r="L58" s="49"/>
     </row>
     <row r="59" spans="1:14">
       <c r="B59" s="71" t="s">
@@ -2861,19 +2706,19 @@
       <c r="L63" s="71"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="B64" s="49" t="s">
+      <c r="B64" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="49"/>
-      <c r="I64" s="49"/>
-      <c r="J64" s="49"/>
-      <c r="K64" s="49"/>
-      <c r="L64" s="49"/>
+      <c r="C64" s="71"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="71"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="71"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="71"/>
+      <c r="L64" s="71"/>
     </row>
     <row r="65" spans="1:14">
       <c r="B65" s="71" t="s">
@@ -2996,19 +2841,19 @@
       <c r="L72" s="71"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="B73" s="71" t="s">
+      <c r="B73" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="71"/>
-      <c r="D73" s="71"/>
-      <c r="E73" s="71"/>
-      <c r="F73" s="71"/>
-      <c r="G73" s="71"/>
-      <c r="H73" s="71"/>
-      <c r="I73" s="71"/>
-      <c r="J73" s="71"/>
-      <c r="K73" s="71"/>
-      <c r="L73" s="71"/>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="67"/>
+      <c r="K73" s="67"/>
+      <c r="L73" s="67"/>
     </row>
     <row r="74" spans="1:14">
       <c r="B74" s="71" t="s">
@@ -3026,62 +2871,34 @@
       <c r="L74" s="71"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="B75" s="71" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">13.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="false"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="7"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve"> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri Light"/>
-              <b val="false"/>
-              <i val="false"/>
-              <strike val="false"/>
-              <color rgb="FF000000"/>
-              <sz val="11"/>
-              <u val="none"/>
-            </rPr>
-            <t xml:space="preserve">Los documentos de importación deber ser entregados a tiempo, de lo contrario, el participante no tendrá opción</t>
-          </r>
-        </is>
-      </c>
-      <c r="C75" s="71"/>
-      <c r="D75" s="71"/>
-      <c r="E75" s="71"/>
-      <c r="F75" s="71"/>
-      <c r="G75" s="71"/>
-      <c r="H75" s="71"/>
-      <c r="I75" s="71"/>
-      <c r="J75" s="71"/>
-      <c r="K75" s="71"/>
-      <c r="L75" s="71"/>
+      <c r="B75" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="67"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="67"/>
+      <c r="H75" s="67"/>
+      <c r="I75" s="67"/>
+      <c r="J75" s="67"/>
+      <c r="K75" s="67"/>
+      <c r="L75" s="67"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="B76" s="67" t="s">
+      <c r="B76" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="C76" s="67"/>
-      <c r="D76" s="67"/>
-      <c r="E76" s="67"/>
-      <c r="F76" s="67"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67"/>
-      <c r="I76" s="67"/>
-      <c r="J76" s="67"/>
-      <c r="K76" s="67"/>
-      <c r="L76" s="67"/>
+      <c r="C76" s="71"/>
+      <c r="D76" s="71"/>
+      <c r="E76" s="71"/>
+      <c r="F76" s="71"/>
+      <c r="G76" s="71"/>
+      <c r="H76" s="71"/>
+      <c r="I76" s="71"/>
+      <c r="J76" s="71"/>
+      <c r="K76" s="71"/>
+      <c r="L76" s="71"/>
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="71" t="s">
@@ -3099,19 +2916,19 @@
       <c r="L77" s="71"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="B78" s="67" t="s">
+      <c r="B78" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="C78" s="67"/>
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="67"/>
-      <c r="I78" s="67"/>
-      <c r="J78" s="67"/>
-      <c r="K78" s="67"/>
-      <c r="L78" s="67"/>
+      <c r="C78" s="71"/>
+      <c r="D78" s="71"/>
+      <c r="E78" s="71"/>
+      <c r="F78" s="71"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="71"/>
+      <c r="I78" s="71"/>
+      <c r="J78" s="71"/>
+      <c r="K78" s="71"/>
+      <c r="L78" s="71"/>
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="71" t="s">
@@ -3144,21 +2961,23 @@
       <c r="L80" s="71"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="B81" s="71" t="s">
+      <c r="A81" s="32"/>
+      <c r="B81" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="C81" s="71"/>
-      <c r="D81" s="71"/>
-      <c r="E81" s="71"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="71"/>
-      <c r="I81" s="71"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="71"/>
-      <c r="L81" s="71"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="72"/>
     </row>
     <row r="82" spans="1:14">
+      <c r="A82" s="32"/>
       <c r="B82" s="71" t="s">
         <v>88</v>
       </c>
@@ -3174,67 +2993,47 @@
       <c r="L82" s="71"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="B83" s="71" t="s">
+      <c r="A83" s="32"/>
+      <c r="B83" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="C83" s="71"/>
-      <c r="D83" s="71"/>
-      <c r="E83" s="71"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="71"/>
-      <c r="I83" s="71"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="71"/>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" s="32"/>
-      <c r="B84" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84" s="72"/>
-      <c r="D84" s="72"/>
-      <c r="E84" s="72"/>
-      <c r="F84" s="72"/>
-      <c r="G84" s="72"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="72"/>
-      <c r="J84" s="72"/>
-      <c r="K84" s="72"/>
-      <c r="L84" s="72"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="72"/>
+      <c r="L83" s="72"/>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="32"/>
-      <c r="B85" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="C85" s="71"/>
-      <c r="D85" s="71"/>
-      <c r="E85" s="71"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="71"/>
-      <c r="I85" s="71"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="71"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38"/>
+      <c r="G85" s="38"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="32"/>
-      <c r="B86" s="72" t="s">
-        <v>92</v>
-      </c>
-      <c r="C86" s="72"/>
-      <c r="D86" s="72"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="72"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="72"/>
-      <c r="L86" s="72"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="38"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38"/>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
     </row>
     <row r="88" spans="1:14">
       <c r="C88" s="38"/>
@@ -3272,7 +3071,7 @@
       <c r="H91" s="38"/>
       <c r="I91" s="38"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" customHeight="1" ht="15.6">
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
@@ -3281,7 +3080,7 @@
       <c r="H92" s="38"/>
       <c r="I92" s="38"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" customHeight="1" ht="15.6">
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
@@ -3299,77 +3098,50 @@
       <c r="H94" s="38"/>
       <c r="I94" s="38"/>
     </row>
-    <row r="95" spans="1:14" customHeight="1" ht="15.6">
-      <c r="C95" s="38"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="38"/>
-      <c r="G95" s="38"/>
-      <c r="H95" s="38"/>
-      <c r="I95" s="38"/>
-    </row>
-    <row r="96" spans="1:14" customHeight="1" ht="15.6">
-      <c r="C96" s="38"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="38"/>
-      <c r="G96" s="38"/>
-      <c r="H96" s="38"/>
-      <c r="I96" s="38"/>
-    </row>
-    <row r="97" spans="1:14">
-      <c r="C97" s="38"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
-      <c r="G97" s="38"/>
-      <c r="H97" s="38"/>
-      <c r="I97" s="38"/>
-    </row>
-    <row r="103" spans="1:14" customHeight="1" ht="15.6"/>
+    <row r="100" spans="1:14" customHeight="1" ht="15.6"/>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="true" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <mergeCells>
-    <mergeCell ref="B76:L76"/>
-    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B74:L74"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="I7:L7"/>
-    <mergeCell ref="B61:L61"/>
-    <mergeCell ref="B50:L50"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B47:L47"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="K38:L38"/>
-    <mergeCell ref="B59:L59"/>
-    <mergeCell ref="B72:L72"/>
-    <mergeCell ref="B60:L60"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B57:L57"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="B86:L86"/>
-    <mergeCell ref="B69:L69"/>
-    <mergeCell ref="B70:L70"/>
-    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B66:L66"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B59:L59"/>
+    <mergeCell ref="B60:L60"/>
+    <mergeCell ref="B61:L61"/>
     <mergeCell ref="B62:L62"/>
     <mergeCell ref="B63:L63"/>
     <mergeCell ref="B64:L64"/>
     <mergeCell ref="B65:L65"/>
-    <mergeCell ref="B66:L66"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B74:L74"/>
+    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B80:L80"/>
     <mergeCell ref="B75:L75"/>
-    <mergeCell ref="B85:L85"/>
-    <mergeCell ref="B84:L84"/>
-    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B77:L77"/>
     <mergeCell ref="B78:L78"/>
     <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="B81:L81"/>
-    <mergeCell ref="B82:L82"/>
-    <mergeCell ref="B52:C56"/>
+    <mergeCell ref="B49:C53"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="B45:L45"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="C37:E37"/>
@@ -3378,7 +3150,7 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="D50:J50"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B26:I26"/>
     <mergeCell ref="B12:L12"/>
@@ -3386,10 +3158,10 @@
     <mergeCell ref="B14:J14"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C88:I97"/>
+    <mergeCell ref="C85:I94"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="E2:L2"/>
-    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="D51:I51"/>
     <mergeCell ref="E3:J3"/>
     <mergeCell ref="E4:J4"/>
     <mergeCell ref="K36:L36"/>
@@ -3399,11 +3171,11 @@
     <mergeCell ref="B34:L34"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B49:L49"/>
-    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="E52:M52"/>
+    <mergeCell ref="K50:M50"/>
+    <mergeCell ref="E49:M49"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B2:C6"/>
     <mergeCell ref="E7:G7"/>
@@ -3430,16 +3202,7 @@
     <mergeCell ref="C42:E42"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="K42:L42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B43:E43"/>
     <mergeCell ref="C8:C9"/>
   </mergeCells>
   <dataValidations count="5">
@@ -3471,7 +3234,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="51" man="1"/>
+    <brk id="48" man="1"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3482,26 +3245,23 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="2" max="2" width="24.708252" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="28.135986" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="26.993408" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="28.135986" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="18.709717" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="28.135986" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="36.419678" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567139" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="17.567139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="18.709717" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="41.132813" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="24.708252" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="12.854004" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="29.421387" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="23.422852" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="18.709717" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="26.993408" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="47.131348" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="12.854004" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:14">
       <c r="B3" s="75" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -3509,9 +3269,9 @@
       <c r="F3" s="74"/>
       <c r="G3" s="74"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:14">
       <c r="B5" s="78" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C5" s="80" t="s">
         <v>49</v>
@@ -3535,216 +3295,166 @@
         <v>55</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="80" t="s">
-        <v>58</v>
-      </c>
-      <c r="M5" s="80" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="74">
+        <v>0</v>
+      </c>
+      <c r="D6" s="74">
+        <v>0</v>
+      </c>
+      <c r="E6" s="74">
+        <v>0</v>
+      </c>
+      <c r="F6" s="74">
+        <v>0</v>
+      </c>
+      <c r="G6" s="74">
+        <v>0</v>
+      </c>
+      <c r="H6" s="74">
+        <v>0</v>
+      </c>
+      <c r="I6" s="74">
+        <v>0</v>
+      </c>
+      <c r="J6" s="82">
+        <v>200</v>
+      </c>
+      <c r="M6" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="N6" s="76" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
-      <c r="B6" s="74" t="s">
+    <row r="7" spans="1:14">
+      <c r="B7" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="74">
-        <v>0</v>
-      </c>
-      <c r="D6" s="74">
-        <v>0</v>
-      </c>
-      <c r="E6" s="74">
-        <v>0</v>
-      </c>
-      <c r="F6" s="74">
-        <v>0</v>
-      </c>
-      <c r="G6" s="74">
-        <v>0</v>
-      </c>
-      <c r="H6" s="74">
-        <v>0</v>
-      </c>
-      <c r="I6" s="74">
-        <v>0</v>
-      </c>
-      <c r="J6" s="74">
-        <v>0</v>
-      </c>
-      <c r="K6" s="74">
-        <v>0</v>
-      </c>
-      <c r="L6" s="74">
-        <v>0</v>
-      </c>
-      <c r="M6" s="82">
-        <v>0</v>
-      </c>
-      <c r="P6" s="76" t="s">
+      <c r="C7" s="74">
+        <v>0</v>
+      </c>
+      <c r="D7" s="74">
+        <v>0</v>
+      </c>
+      <c r="E7" s="74">
+        <v>0</v>
+      </c>
+      <c r="F7" s="74">
+        <v>0</v>
+      </c>
+      <c r="G7" s="74">
+        <v>0</v>
+      </c>
+      <c r="H7" s="74">
+        <v>0</v>
+      </c>
+      <c r="I7" s="74">
+        <v>0</v>
+      </c>
+      <c r="J7" s="83">
+        <v>0.91</v>
+      </c>
+      <c r="M7" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="77">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="76" t="s">
+      <c r="C8" s="81">
+        <v>3.2</v>
+      </c>
+      <c r="D8" s="81">
+        <v>6.9</v>
+      </c>
+      <c r="E8" s="81">
+        <v>5.75</v>
+      </c>
+      <c r="F8" s="81">
+        <v>1</v>
+      </c>
+      <c r="G8" s="81">
+        <v>2.18</v>
+      </c>
+      <c r="H8" s="81">
+        <v>1.3071428571429</v>
+      </c>
+      <c r="I8" s="81">
+        <v>208</v>
+      </c>
+      <c r="J8" s="74"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" s="79" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="B7" s="74" t="s">
+      <c r="C9" s="81">
+        <v>0</v>
+      </c>
+      <c r="D9" s="81">
+        <v>0</v>
+      </c>
+      <c r="E9" s="81">
+        <v>0</v>
+      </c>
+      <c r="F9" s="81">
+        <v>0</v>
+      </c>
+      <c r="G9" s="81">
+        <v>0</v>
+      </c>
+      <c r="H9" s="81">
+        <v>0</v>
+      </c>
+      <c r="I9" s="81">
+        <v>0</v>
+      </c>
+      <c r="J9" s="74"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="74">
-        <v>0</v>
-      </c>
-      <c r="D7" s="74">
-        <v>0</v>
-      </c>
-      <c r="E7" s="74">
-        <v>0</v>
-      </c>
-      <c r="F7" s="74">
-        <v>0</v>
-      </c>
-      <c r="G7" s="74">
-        <v>0</v>
-      </c>
-      <c r="H7" s="74">
-        <v>0</v>
-      </c>
-      <c r="I7" s="74">
-        <v>0</v>
-      </c>
-      <c r="J7" s="74">
-        <v>0</v>
-      </c>
-      <c r="K7" s="74">
-        <v>0</v>
-      </c>
-      <c r="L7" s="74">
-        <v>0</v>
-      </c>
-      <c r="M7" s="83"/>
-      <c r="P7" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q7" s="77"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="B8" s="74" t="s">
+      <c r="C10" s="74">
+        <v>25</v>
+      </c>
+      <c r="D10" s="74">
+        <v>20</v>
+      </c>
+      <c r="E10" s="74">
+        <v>20</v>
+      </c>
+      <c r="F10" s="74">
+        <v>120</v>
+      </c>
+      <c r="G10" s="74">
+        <v>200</v>
+      </c>
+      <c r="H10" s="74">
+        <v>525</v>
+      </c>
+      <c r="I10" s="74">
+        <v>1</v>
+      </c>
+      <c r="J10" s="74" t="str">
+        <f>SUM(C10:I10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="74" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" s="81">
-        <v>1.8</v>
-      </c>
-      <c r="D8" s="81">
-        <v>1.3884615384615</v>
-      </c>
-      <c r="E8" s="81">
-        <v>7.9</v>
-      </c>
-      <c r="F8" s="81">
-        <v>9.2</v>
-      </c>
-      <c r="G8" s="81">
-        <v>8.6</v>
-      </c>
-      <c r="H8" s="81">
-        <v>4.6</v>
-      </c>
-      <c r="I8" s="81">
-        <v>1.1285714285714</v>
-      </c>
-      <c r="J8" s="81">
-        <v>1.2</v>
-      </c>
-      <c r="K8" s="81">
-        <v>2.3</v>
-      </c>
-      <c r="L8" s="81">
-        <v>0.85</v>
-      </c>
-      <c r="M8" s="74"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="B9" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="81">
-        <v>0</v>
-      </c>
-      <c r="D9" s="81">
-        <v>0</v>
-      </c>
-      <c r="E9" s="81">
-        <v>0</v>
-      </c>
-      <c r="F9" s="81">
-        <v>0</v>
-      </c>
-      <c r="G9" s="81">
-        <v>0</v>
-      </c>
-      <c r="H9" s="81">
-        <v>0</v>
-      </c>
-      <c r="I9" s="81">
-        <v>0</v>
-      </c>
-      <c r="J9" s="81">
-        <v>0</v>
-      </c>
-      <c r="K9" s="81">
-        <v>0</v>
-      </c>
-      <c r="L9" s="81">
-        <v>0</v>
-      </c>
-      <c r="M9" s="74"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="B10" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="74">
-        <v>150</v>
-      </c>
-      <c r="D10" s="74">
-        <v>650</v>
-      </c>
-      <c r="E10" s="74">
-        <v>15</v>
-      </c>
-      <c r="F10" s="74">
-        <v>20</v>
-      </c>
-      <c r="G10" s="74">
-        <v>20</v>
-      </c>
-      <c r="H10" s="74">
-        <v>40</v>
-      </c>
-      <c r="I10" s="74">
-        <v>350</v>
-      </c>
-      <c r="J10" s="74">
-        <v>50</v>
-      </c>
-      <c r="K10" s="74">
-        <v>70</v>
-      </c>
-      <c r="L10" s="74">
-        <v>150</v>
-      </c>
-      <c r="M10" s="74" t="str">
-        <f>SUM(C10:L10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="B11" s="74" t="s">
-        <v>103</v>
       </c>
       <c r="C11" s="81" t="str">
         <f>C8*C10</f>
@@ -3774,26 +3484,14 @@
         <f>I8*I10</f>
         <v>0</v>
       </c>
-      <c r="J11" s="81" t="str">
-        <f>J8*J10</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="81" t="str">
-        <f>K8*K10</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="81" t="str">
-        <f>L8*L10</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="86" t="str">
-        <f>SUM(C11:L11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="J11" s="86" t="str">
+        <f>SUM(C11:I11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C12" s="81" t="str">
         <f>C10*C9</f>
@@ -3823,374 +3521,278 @@
         <f>I10*I9</f>
         <v>0</v>
       </c>
-      <c r="J12" s="81" t="str">
-        <f>J10*J9</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="81" t="str">
-        <f>K10*K9</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="81" t="str">
-        <f>L10*L9</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="86" t="str">
-        <f>SUM(C12:L12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="J12" s="86" t="str">
+        <f>SUM(C12:I12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="84" t="str">
+        <f>C11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="84" t="str">
+        <f>D11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="84" t="str">
+        <f>E11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="84" t="str">
+        <f>F11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="84" t="str">
+        <f>G11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="84" t="str">
+        <f>H11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="84" t="str">
+        <f>I11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="74"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="81" t="str">
+        <f>J14*C13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="81" t="str">
+        <f>J14*D13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="81" t="str">
+        <f>J14*E13</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="81" t="str">
+        <f>J14*F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="81" t="str">
+        <f>J14*G13</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="81" t="str">
+        <f>J14*H13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="81" t="str">
+        <f>J14*I13</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="86" t="str">
+        <f>IF(J7&lt;1, N7*0.6, N7*0.6*J7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="81" t="str">
+        <f>C11+C14</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="81" t="str">
+        <f>D11+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="81" t="str">
+        <f>E11+E14</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="81" t="str">
+        <f>F11+F14</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="81" t="str">
+        <f>G11+G14</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="81" t="str">
+        <f>H11+H14</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="81" t="str">
+        <f>I11+I14</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="86" t="str">
+        <f>SUM(C15:I15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="84" t="str">
-        <f>C11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="84" t="str">
-        <f>D11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="84" t="str">
-        <f>E11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="84" t="str">
-        <f>F11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="84" t="str">
-        <f>G11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="84" t="str">
-        <f>H11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="84" t="str">
-        <f>I11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="84" t="str">
-        <f>J11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="84" t="str">
-        <f>K11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="84" t="str">
-        <f>L11/M11</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="74"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="B14" s="74" t="s">
+      <c r="C16" s="81" t="str">
+        <f>C12+C14</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="81" t="str">
+        <f>D12+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="81" t="str">
+        <f>E12+E14</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="81" t="str">
+        <f>F12+F14</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="81" t="str">
+        <f>G12+G14</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="81" t="str">
+        <f>H12+H14</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="81" t="str">
+        <f>I12+I14</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="86" t="str">
+        <f>SUM(C16:I16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="B17" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="81" t="str">
-        <f>ROUNDUP(M14*C13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="81" t="str">
-        <f>ROUNDUP(M14*D13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="81" t="str">
-        <f>ROUNDUP(M14*E13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="81" t="str">
-        <f>ROUNDUP(M14*F13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="81" t="str">
-        <f>ROUNDUP(M14*G13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="81" t="str">
-        <f>ROUNDUP(M14*H13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="81" t="str">
-        <f>ROUNDUP(M14*I13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="81" t="str">
-        <f>ROUNDUP(M14*J13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="81" t="str">
-        <f>ROUNDUP(M14*K13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="81" t="str">
-        <f>ROUNDUP(M14*L13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="86" t="str">
-        <f>IF(M7&lt;1, ROUNDUP(Q7*0.6, 0), ROUNDUP(Q7*0.6*M7, 0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="B15" s="74" t="s">
+      <c r="C17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*C13,50*C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*D13,50*D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*E13,50*E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*F13,50*F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*G13,50*G13)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*H13,50*H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="81" t="str">
+        <f>IF(J15&gt;5000,100*I13,50*I13)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="86" t="str">
+        <f>SUM(C17:I17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="B18" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="81" t="str">
-        <f>ROUNDUP(C11+C14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="81" t="str">
-        <f>ROUNDUP(D11+D14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="81" t="str">
-        <f>ROUNDUP(E11+E14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="81" t="str">
-        <f>ROUNDUP(F11+F14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="81" t="str">
-        <f>ROUNDUP(G11+G14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="81" t="str">
-        <f>ROUNDUP(H11+H14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="81" t="str">
-        <f>ROUNDUP(I11+I14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="81" t="str">
-        <f>ROUNDUP(J11+J14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="81" t="str">
-        <f>ROUNDUP(K11+K14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="81" t="str">
-        <f>ROUNDUP(L11+L14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="86" t="str">
-        <f>SUM(C15:L15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="B16" s="79" t="s">
+      <c r="C18" s="81" t="str">
+        <f>C15+C17</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="81" t="str">
+        <f>D15+D17</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="81" t="str">
+        <f>E15+E17</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="81" t="str">
+        <f>F15+F17</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="81" t="str">
+        <f>G15+G17</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="81" t="str">
+        <f>H15+H17</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="81" t="str">
+        <f>I15+I17</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="86" t="str">
+        <f>SUM(C18:I18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="B19" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="81" t="str">
-        <f>ROUNDUP(C12+C14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="81" t="str">
-        <f>ROUNDUP(D12+D14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="81" t="str">
-        <f>ROUNDUP(E12+E14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="81" t="str">
-        <f>ROUNDUP(F12+F14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="81" t="str">
-        <f>ROUNDUP(G12+G14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="81" t="str">
-        <f>ROUNDUP(H12+H14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="81" t="str">
-        <f>ROUNDUP(I12+I14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="81" t="str">
-        <f>ROUNDUP(J12+J14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="81" t="str">
-        <f>ROUNDUP(K12+K14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="81" t="str">
-        <f>ROUNDUP(L12+L14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="86" t="str">
-        <f>SUM(C16:L16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="B17" s="74" t="s">
+      <c r="C19" s="81" t="str">
+        <f>C16+C17</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="81" t="str">
+        <f>D16+D17</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="81" t="str">
+        <f>E16+E17</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="81" t="str">
+        <f>F16+F17</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="81" t="str">
+        <f>G16+G17</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="81" t="str">
+        <f>H16+H17</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="81" t="str">
+        <f>I16+I17</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="86" t="str">
+        <f>SUM(C19:I19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="B23" s="75" t="s">
         <v>109</v>
-      </c>
-      <c r="C17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*D13,2),ROUND(50*D13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*E13,2),ROUND(50*E13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*F13,2),ROUND(50*F13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*G13,2),ROUND(50*G13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*H13,2),ROUND(50*H13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*I13,2),ROUND(50*I13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*J13,2),ROUND(50*J13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*K13,2),ROUND(50*K13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="81" t="str">
-        <f>IF(M15&gt;5000,ROUND(100*L13,2),ROUND(50*L13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="86" t="str">
-        <f>SUM(C17:L17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="B18" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="81" t="str">
-        <f>ROUNDUP(C15+C17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="81" t="str">
-        <f>ROUNDUP(D15+D17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="81" t="str">
-        <f>ROUNDUP(E15+E17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="81" t="str">
-        <f>ROUNDUP(F15+F17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="81" t="str">
-        <f>ROUNDUP(G15+G17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="81" t="str">
-        <f>ROUNDUP(H15+H17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="81" t="str">
-        <f>ROUNDUP(I15+I17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="81" t="str">
-        <f>ROUNDUP(J15+J17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="81" t="str">
-        <f>ROUNDUP(K15+K17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="81" t="str">
-        <f>ROUNDUP(L15+L17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="86" t="str">
-        <f>SUM(C18:L18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="B19" s="79" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="81" t="str">
-        <f>ROUNDUP(C16+C17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="81" t="str">
-        <f>ROUNDUP(D16+D17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="81" t="str">
-        <f>ROUNDUP(E16+E17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="81" t="str">
-        <f>ROUNDUP(F16+F17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="81" t="str">
-        <f>ROUNDUP(G16+G17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="81" t="str">
-        <f>ROUNDUP(H16+H17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="81" t="str">
-        <f>ROUNDUP(I16+I17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="81" t="str">
-        <f>ROUNDUP(J16+J17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="81" t="str">
-        <f>ROUNDUP(K16+K17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="81" t="str">
-        <f>ROUNDUP(L16+L17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="86" t="str">
-        <f>SUM(C19:L19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="B23" s="75" t="s">
-        <v>112</v>
       </c>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
       <c r="E23" s="74"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:14">
       <c r="B26" s="74" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C26" s="81">
         <v>0</v>
@@ -4213,21 +3815,12 @@
       <c r="I26" s="81">
         <v>0</v>
       </c>
-      <c r="J26" s="81">
-        <v>0</v>
-      </c>
-      <c r="K26" s="81">
-        <v>0</v>
-      </c>
-      <c r="L26" s="81">
-        <v>0</v>
-      </c>
-      <c r="M26" s="81" t="str">
-        <f>SUM(C26:L26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="J26" s="81" t="str">
+        <f>SUM(C26:I26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="C27" s="87">
         <v>0</v>
       </c>
@@ -4249,23 +3842,14 @@
       <c r="I27" s="87">
         <v>0</v>
       </c>
-      <c r="J27" s="87">
-        <v>0</v>
-      </c>
-      <c r="K27" s="87">
-        <v>0</v>
-      </c>
-      <c r="L27" s="87">
-        <v>0</v>
-      </c>
-      <c r="M27" s="84" t="str">
-        <f>SUM(C27:L27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="J27" s="84" t="str">
+        <f>SUM(C27:I27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="B28" s="74" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C28" s="81" t="str">
         <f>MAX(C19,C18)*C27</f>
@@ -4296,23 +3880,11 @@
         <v>0</v>
       </c>
       <c r="J28" s="81" t="str">
-        <f>MAX(J19,J18)*J27</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="81" t="str">
-        <f>MAX(K19,K18)*K27</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="81" t="str">
-        <f>MAX(L19,L18)*L27</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="81" t="str">
-        <f>SUM(C28:L28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
+        <f>SUM(C28:I28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="B29" s="74" t="s">
         <v>31</v>
       </c>
@@ -4345,23 +3917,11 @@
         <v>0</v>
       </c>
       <c r="J29" s="81" t="str">
-        <f>0.16*(MAX(J19,J18)+J28)</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="81" t="str">
-        <f>0.16*(MAX(K19,K18)+K28)</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="81" t="str">
-        <f>0.16*(MAX(L19,L18)+L28)</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="81" t="str">
-        <f>SUM(C29:L29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
+        <f>SUM(C29:I29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="B30" s="74" t="s">
         <v>32</v>
       </c>
@@ -4394,25 +3954,13 @@
         <v>0</v>
       </c>
       <c r="J30" s="81" t="str">
-        <f>0.02*(MAX(J19,J18)+J28)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="81" t="str">
-        <f>0.02*(MAX(K19,K18)+K28)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="81" t="str">
-        <f>0.02*(MAX(L19,L18)+L28)</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="81" t="str">
-        <f>SUM(C30:L30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
+        <f>SUM(C30:I30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="B31" s="74" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C31" s="81" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
@@ -4443,23 +3991,11 @@
         <v>0</v>
       </c>
       <c r="J31" s="81" t="str">
-        <f>0.035*(MAX(J18,J19) +J28+J29+J30)</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="81" t="str">
-        <f>0.035*(MAX(K18,K19) +K28+K29+K30)</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="81" t="str">
-        <f>0.035*(MAX(L18,L19) +L28+L29+L30)</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="81" t="str">
-        <f>SUM(C31:L31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
+        <f>SUM(C31:I31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="B32" s="74" t="s">
         <v>36</v>
       </c>
@@ -4495,82 +4031,58 @@
         <f>SUM(J28:J31)</f>
         <v>0</v>
       </c>
-      <c r="K32" s="81" t="str">
-        <f>SUM(K28:K31)</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="81" t="str">
-        <f>SUM(L28:L31)</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="81" t="str">
-        <f>SUM(M28:M31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
+    </row>
+    <row r="37" spans="1:14">
       <c r="B37" s="75" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
       <c r="E37" s="74"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:14">
       <c r="B40" s="74" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C40" s="81" t="str">
-        <f>C13*M40</f>
+        <f>C13*J40</f>
         <v>0</v>
       </c>
       <c r="D40" s="81" t="str">
-        <f>D13*M40</f>
+        <f>D13*J40</f>
         <v>0</v>
       </c>
       <c r="E40" s="81" t="str">
-        <f>E13*M40</f>
+        <f>E13*J40</f>
         <v>0</v>
       </c>
       <c r="F40" s="81" t="str">
-        <f>F13*M40</f>
+        <f>F13*J40</f>
         <v>0</v>
       </c>
       <c r="G40" s="81" t="str">
-        <f>G13*M40</f>
+        <f>G13*J40</f>
         <v>0</v>
       </c>
       <c r="H40" s="81" t="str">
-        <f>H13*M40</f>
+        <f>H13*J40</f>
         <v>0</v>
       </c>
       <c r="I40" s="81" t="str">
-        <f>I13*M40</f>
+        <f>I13*J40</f>
         <v>0</v>
       </c>
       <c r="J40" s="81" t="str">
-        <f>J13*M40</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="81" t="str">
-        <f>K13*M40</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="81" t="str">
-        <f>L13*M40</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="81" t="str">
-        <f>IF(M7&lt;1, ROUNDUP(Q7*0.4, 0), ROUNDUP(Q7*0.4*M7, 0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
+        <f>IF(J7&lt;1, N7*0.4,N7*0.4*J7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="B41"/>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:14">
       <c r="B43" s="74" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C43" s="74" t="s">
         <v>49</v>
@@ -4594,194 +4106,140 @@
         <v>55</v>
       </c>
       <c r="J43" s="74" t="s">
-        <v>56</v>
-      </c>
-      <c r="K43" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="L43" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="M43" s="74" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="B44" s="74" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C44" s="81" t="str">
-        <f>SUM(C15,C40,C32,(C26*C10))</f>
+        <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
       <c r="D44" s="81" t="str">
-        <f>SUM(D15,D40,D32,(D26*D10))</f>
+        <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
       <c r="E44" s="81" t="str">
-        <f>SUM(E15,E40,E32,(E26*E10))</f>
+        <f>SUM(E15,E40,E32,(E26))</f>
         <v>0</v>
       </c>
       <c r="F44" s="81" t="str">
-        <f>SUM(F15,F40,F32,(F26*F10))</f>
+        <f>SUM(F15,F40,F32,(F26))</f>
         <v>0</v>
       </c>
       <c r="G44" s="81" t="str">
-        <f>SUM(G15,G40,G32,(G26*G10))</f>
+        <f>SUM(G15,G40,G32,(G26))</f>
         <v>0</v>
       </c>
       <c r="H44" s="81" t="str">
-        <f>SUM(H15,H40,H32,(H26*H10))</f>
+        <f>SUM(H15,H40,H32,(H26))</f>
         <v>0</v>
       </c>
       <c r="I44" s="81" t="str">
-        <f>SUM(I15,I40,I32,(I26*I10))</f>
+        <f>SUM(I15,I40,I32,(I26))</f>
         <v>0</v>
       </c>
       <c r="J44" s="81" t="str">
-        <f>SUM(J15,J40,J32,(J26*J10))</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="81" t="str">
-        <f>SUM(K15,K40,K32,(K26*K10))</f>
-        <v>0</v>
-      </c>
-      <c r="L44" s="81" t="str">
-        <f>SUM(L15,L40,L32,(L26*L10))</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="81" t="str">
-        <f>SUM(C44:L44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17">
+        <f>SUM(C44:I44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="B45" s="74" t="s">
         <v>45</v>
       </c>
       <c r="C45" s="74">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="D45" s="74">
-        <v>650</v>
+        <v>20</v>
       </c>
       <c r="E45" s="74">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F45" s="74">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G45" s="74">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="H45" s="74">
-        <v>40</v>
+        <v>525</v>
       </c>
       <c r="I45" s="74">
-        <v>350</v>
-      </c>
-      <c r="J45" s="74">
-        <v>50</v>
-      </c>
-      <c r="K45" s="74">
-        <v>70</v>
-      </c>
-      <c r="L45" s="74">
-        <v>150</v>
-      </c>
-      <c r="M45" s="74"/>
-    </row>
-    <row r="46" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="J45" s="74"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="B46" s="74" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C46" s="81" t="str">
-        <f>ROUND(SUM(C44/C45),2)</f>
+        <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="81" t="str">
-        <f>ROUND(SUM(D44/D45),2)</f>
+        <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="81" t="str">
-        <f>ROUND(SUM(E44/E45),2)</f>
+        <f>SUM(E44/E45)</f>
         <v>0</v>
       </c>
       <c r="F46" s="81" t="str">
-        <f>ROUND(SUM(F44/F45),2)</f>
+        <f>SUM(F44/F45)</f>
         <v>0</v>
       </c>
       <c r="G46" s="81" t="str">
-        <f>ROUND(SUM(G44/G45),2)</f>
+        <f>SUM(G44/G45)</f>
         <v>0</v>
       </c>
       <c r="H46" s="81" t="str">
-        <f>ROUND(SUM(H44/H45),2)</f>
+        <f>SUM(H44/H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="81" t="str">
-        <f>ROUND(SUM(I44/I45),2)</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="81" t="str">
-        <f>ROUND(SUM(J44/J45),2)</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="81" t="str">
-        <f>ROUND(SUM(K44/K45),2)</f>
-        <v>0</v>
-      </c>
-      <c r="L46" s="81" t="str">
-        <f>ROUND(SUM(L44/L45),2)</f>
-        <v>0</v>
-      </c>
-      <c r="M46" s="74"/>
-    </row>
-    <row r="47" spans="1:17">
+        <f>SUM(I44/I45)</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="74"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="B47" s="74" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C47" s="85" t="str">
-        <f>ROUND(C46*3.7,2)</f>
+        <f>C46*3.7</f>
         <v>0</v>
       </c>
       <c r="D47" s="85" t="str">
-        <f>ROUND(D46*3.7,2)</f>
+        <f>D46*3.7</f>
         <v>0</v>
       </c>
       <c r="E47" s="85" t="str">
-        <f>ROUND(E46*3.7,2)</f>
+        <f>E46*3.7</f>
         <v>0</v>
       </c>
       <c r="F47" s="85" t="str">
-        <f>ROUND(F46*3.7,2)</f>
+        <f>F46*3.7</f>
         <v>0</v>
       </c>
       <c r="G47" s="85" t="str">
-        <f>ROUND(G46*3.7,2)</f>
+        <f>G46*3.7</f>
         <v>0</v>
       </c>
       <c r="H47" s="85" t="str">
-        <f>ROUND(H46*3.7,2)</f>
+        <f>H46*3.7</f>
         <v>0</v>
       </c>
       <c r="I47" s="85" t="str">
-        <f>ROUND(I46*3.7,2)</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="85" t="str">
-        <f>ROUND(J46*3.7,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="85" t="str">
-        <f>ROUND(K46*3.7,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L47" s="85" t="str">
-        <f>ROUND(L46*3.7,2)</f>
-        <v>0</v>
-      </c>
-      <c r="M47" s="74"/>
+        <f>I46*3.7</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="74"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/assets/downloads/CotizacionVICTOR LUIS SAN MIGUEL CASAS.xlsx
+++ b/assets/downloads/CotizacionVICTOR LUIS SAN MIGUEL CASAS.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -53,7 +53,7 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>200 Kg</t>
+    <t>800 Kg</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
@@ -71,10 +71,13 @@
     <t>TELEFONO:</t>
   </si>
   <si>
+    <t>51 956 686 057</t>
+  </si>
+  <si>
     <t>CLIENTE:</t>
   </si>
   <si>
-    <t>ANTIGUO</t>
+    <t>MANUAL</t>
   </si>
   <si>
     <t>CBM</t>
@@ -113,9 +116,9 @@
     <t>Hola VICTOR LUIS SAN MIGUEL CASAS 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $415.8
-        ☑️Impuestos: $452.17
-        ☑️ Total: $867.97
+        ☑️Costo CBM: $382.39344
+        ☑️Impuestos: $2207.65
+        ☑️ Total: $2590.04344
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -174,25 +177,25 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>MOCHILA DE HIDRATACION</t>
-  </si>
-  <si>
-    <t>MOCHILA TACTICA MILITAR</t>
-  </si>
-  <si>
-    <t>LONCHERA TACTICA MILITAR</t>
+    <t>CASACA TACTICA MILITAR</t>
+  </si>
+  <si>
+    <t>PANTALON TACTICO MILITAR</t>
+  </si>
+  <si>
+    <t>PULSERA MULTIFUNCIONAL 5 EN 1</t>
   </si>
   <si>
     <t>PASAMONTAÑA MILITAR</t>
   </si>
   <si>
-    <t>GUANTES MILITAR</t>
-  </si>
-  <si>
-    <t>GUANTES CORTOS MILITAR</t>
-  </si>
-  <si>
-    <t>MAQUINA DE SUBLIMACION DE TRANSFERENCIA</t>
+    <t>GORRO TACTICO MILITAR</t>
+  </si>
+  <si>
+    <t>CAMISETA TACTICA MILITAR</t>
+  </si>
+  <si>
+    <t>CAMISETA MANGA LARGA MILITAR</t>
   </si>
   <si>
     <r>
@@ -1708,7 +1711,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="16">
-        <v>10741433066</v>
+        <v>74143306</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="27" t="s">
@@ -1730,20 +1733,20 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17">
-        <v>51956686057</v>
+      <c r="C11" s="17" t="s">
+        <v>17</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="65"/>
       <c r="H11" s="33"/>
       <c r="I11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="95" t="str">
         <f>'2'!J7</f>
@@ -1767,7 +1770,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -1778,15 +1781,15 @@
       <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="67"/>
@@ -1801,12 +1804,12 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -1821,12 +1824,12 @@
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
@@ -1841,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1872,7 +1875,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
@@ -1882,18 +1885,18 @@
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -1911,15 +1914,15 @@
         <v>0</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -1936,12 +1939,12 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="48"/>
@@ -1958,12 +1961,12 @@
         <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -1978,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1996,7 +1999,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="48"/>
@@ -2006,19 +2009,19 @@
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="J25" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15" t="str">
         <f>'2'!J31</f>
         <v>0</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
@@ -2032,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2047,7 +2050,7 @@
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="15.6">
       <c r="B28" s="52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="52"/>
       <c r="D28" s="52"/>
@@ -2058,15 +2061,15 @@
       <c r="I28" s="52"/>
       <c r="J28" s="52"/>
       <c r="K28" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="B29" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="49"/>
       <c r="D29" s="49"/>
@@ -2081,12 +2084,12 @@
         <v>0</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -2101,12 +2104,12 @@
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="48"/>
@@ -2121,12 +2124,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
@@ -2141,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2159,7 +2162,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="B34" s="59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
@@ -2174,28 +2177,28 @@
     </row>
     <row r="35" spans="1:14">
       <c r="B35" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" s="57"/>
       <c r="E35" s="58"/>
       <c r="F35" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L35" s="47"/>
     </row>
@@ -2204,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -2237,7 +2240,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2270,7 +2273,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2303,7 +2306,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2336,7 +2339,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2368,7 +2371,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -2400,7 +2403,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2429,7 +2432,7 @@
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="18">
       <c r="B43" s="93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C43" s="92"/>
       <c r="D43" s="92"/>
@@ -2450,7 +2453,7 @@
     </row>
     <row r="44" spans="1:14" customHeight="1" ht="18">
       <c r="B44" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C44" s="64"/>
       <c r="D44" s="64"/>
@@ -2465,7 +2468,7 @@
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="18">
       <c r="B45" s="64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C45" s="64"/>
       <c r="D45" s="64"/>
@@ -2480,7 +2483,7 @@
     </row>
     <row r="46" spans="1:14" customHeight="1" ht="18">
       <c r="B46" s="64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C46" s="64"/>
       <c r="D46" s="64"/>
@@ -2495,7 +2498,7 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="18">
       <c r="B47" s="64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C47" s="64"/>
       <c r="D47" s="64"/>
@@ -2554,7 +2557,7 @@
       <c r="B51" s="38"/>
       <c r="C51" s="38"/>
       <c r="D51" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E51" s="53"/>
       <c r="F51" s="53"/>
@@ -2572,7 +2575,7 @@
     </row>
     <row r="54" spans="1:14" customHeight="1" ht="21">
       <c r="B54" s="70" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C54" s="70"/>
       <c r="D54" s="70"/>
@@ -2587,7 +2590,7 @@
     </row>
     <row r="56" spans="1:14">
       <c r="B56" s="71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="71"/>
       <c r="D56" s="71"/>
@@ -2602,7 +2605,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="B57" s="71" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="71"/>
       <c r="D57" s="71"/>
@@ -2617,7 +2620,7 @@
     </row>
     <row r="58" spans="1:14">
       <c r="B58" s="49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="49"/>
       <c r="D58" s="49"/>
@@ -2632,7 +2635,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="B59" s="71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="71"/>
       <c r="D59" s="71"/>
@@ -2647,7 +2650,7 @@
     </row>
     <row r="60" spans="1:14">
       <c r="B60" s="71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="71"/>
       <c r="D60" s="71"/>
@@ -2662,7 +2665,7 @@
     </row>
     <row r="61" spans="1:14">
       <c r="B61" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C61" s="49"/>
       <c r="D61" s="49"/>
@@ -2677,7 +2680,7 @@
     </row>
     <row r="62" spans="1:14">
       <c r="B62" s="71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" s="71"/>
       <c r="D62" s="71"/>
@@ -2692,7 +2695,7 @@
     </row>
     <row r="63" spans="1:14">
       <c r="B63" s="71" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" s="71"/>
       <c r="D63" s="71"/>
@@ -2707,7 +2710,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="B64" s="71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="71"/>
       <c r="D64" s="71"/>
@@ -2722,7 +2725,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="B65" s="71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="71"/>
       <c r="D65" s="71"/>
@@ -2737,7 +2740,7 @@
     </row>
     <row r="66" spans="1:14">
       <c r="B66" s="71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="71"/>
       <c r="D66" s="71"/>
@@ -2752,7 +2755,7 @@
     </row>
     <row r="67" spans="1:14">
       <c r="B67" s="71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" s="71"/>
       <c r="D67" s="71"/>
@@ -2767,7 +2770,7 @@
     </row>
     <row r="68" spans="1:14">
       <c r="B68" s="71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68" s="71"/>
       <c r="D68" s="71"/>
@@ -2782,7 +2785,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" s="71"/>
       <c r="D69" s="71"/>
@@ -2797,7 +2800,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="B70" s="71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="71"/>
       <c r="D70" s="71"/>
@@ -2812,7 +2815,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="B71" s="71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71" s="71"/>
       <c r="D71" s="71"/>
@@ -2827,7 +2830,7 @@
     </row>
     <row r="72" spans="1:14">
       <c r="B72" s="71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72" s="71"/>
       <c r="D72" s="71"/>
@@ -2842,7 +2845,7 @@
     </row>
     <row r="73" spans="1:14">
       <c r="B73" s="67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" s="67"/>
       <c r="D73" s="67"/>
@@ -2857,7 +2860,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="B74" s="71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="71"/>
       <c r="D74" s="71"/>
@@ -2872,7 +2875,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="B75" s="67" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="67"/>
       <c r="D75" s="67"/>
@@ -2887,7 +2890,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="B76" s="71" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="71"/>
       <c r="D76" s="71"/>
@@ -2902,7 +2905,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="71"/>
       <c r="D77" s="71"/>
@@ -2917,7 +2920,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="71"/>
       <c r="D78" s="71"/>
@@ -2932,7 +2935,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="71"/>
       <c r="D79" s="71"/>
@@ -2947,7 +2950,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="B80" s="71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="71"/>
       <c r="D80" s="71"/>
@@ -2963,7 +2966,7 @@
     <row r="81" spans="1:14">
       <c r="A81" s="32"/>
       <c r="B81" s="72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="72"/>
       <c r="D81" s="72"/>
@@ -2979,7 +2982,7 @@
     <row r="82" spans="1:14">
       <c r="A82" s="32"/>
       <c r="B82" s="71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="71"/>
       <c r="D82" s="71"/>
@@ -2995,7 +2998,7 @@
     <row r="83" spans="1:14">
       <c r="A83" s="32"/>
       <c r="B83" s="72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="72"/>
       <c r="D83" s="72"/>
@@ -3250,18 +3253,18 @@
   <cols>
     <col min="2" max="2" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="26.993408" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="28.135986" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="29.421387" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="29.421387" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="35.2771" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="23.422852" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="18.709717" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="26.993408" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="47.131348" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.85083" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="29.421387" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="34.134521" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="12.854004" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:14">
       <c r="B3" s="75" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -3271,36 +3274,36 @@
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I5" s="80" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="74" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="74">
         <v>0</v>
@@ -3324,18 +3327,18 @@
         <v>0</v>
       </c>
       <c r="J6" s="82">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="M6" s="76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N6" s="76" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="74" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="74">
         <v>0</v>
@@ -3359,45 +3362,45 @@
         <v>0</v>
       </c>
       <c r="J7" s="83">
-        <v>0.91</v>
+        <v>2.55</v>
       </c>
       <c r="M7" s="77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="77">
-        <v>350</v>
+        <v>321.88</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="B8" s="74" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="81">
-        <v>3.2</v>
+        <v>9.44775</v>
       </c>
       <c r="D8" s="81">
-        <v>6.9</v>
+        <v>8.2386877828054</v>
       </c>
       <c r="E8" s="81">
-        <v>5.75</v>
+        <v>0.76</v>
       </c>
       <c r="F8" s="81">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="G8" s="81">
-        <v>2.18</v>
+        <v>1.2182608695652</v>
       </c>
       <c r="H8" s="81">
-        <v>1.3071428571429</v>
+        <v>2.5</v>
       </c>
       <c r="I8" s="81">
-        <v>208</v>
+        <v>7.4</v>
       </c>
       <c r="J8" s="74"/>
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="81">
         <v>0</v>
@@ -3424,28 +3427,28 @@
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="74" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" s="74">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D10" s="74">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="E10" s="74">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F10" s="74">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="G10" s="74">
-        <v>200</v>
+        <v>460</v>
       </c>
       <c r="H10" s="74">
-        <v>525</v>
+        <v>51</v>
       </c>
       <c r="I10" s="74">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="J10" s="74" t="str">
         <f>SUM(C10:I10)</f>
@@ -3454,7 +3457,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="74" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="81" t="str">
         <f>C8*C10</f>
@@ -3491,7 +3494,7 @@
     </row>
     <row r="12" spans="1:14">
       <c r="B12" s="79" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="81" t="str">
         <f>C10*C9</f>
@@ -3528,7 +3531,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="74" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="84" t="str">
         <f>C11/J11</f>
@@ -3562,7 +3565,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="81" t="str">
         <f>J14*C13</f>
@@ -3599,7 +3602,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="81" t="str">
         <f>C11+C14</f>
@@ -3636,7 +3639,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="79" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="81" t="str">
         <f>C12+C14</f>
@@ -3673,34 +3676,34 @@
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="74" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*C13,50*C13)</f>
+        <f>IF(J11&gt;5000,100*C13,50*C13)</f>
         <v>0</v>
       </c>
       <c r="D17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*D13,50*D13)</f>
+        <f>IF(J11&gt;5000,100*D13,50*D13)</f>
         <v>0</v>
       </c>
       <c r="E17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*E13,50*E13)</f>
+        <f>IF(J11&gt;5000,100*E13,50*E13)</f>
         <v>0</v>
       </c>
       <c r="F17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*F13,50*F13)</f>
+        <f>IF(J11&gt;5000,100*F13,50*F13)</f>
         <v>0</v>
       </c>
       <c r="G17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*G13,50*G13)</f>
+        <f>IF(J11&gt;5000,100*G13,50*G13)</f>
         <v>0</v>
       </c>
       <c r="H17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*H13,50*H13)</f>
+        <f>IF(J11&gt;5000,100*H13,50*H13)</f>
         <v>0</v>
       </c>
       <c r="I17" s="81" t="str">
-        <f>IF(J15&gt;5000,100*I13,50*I13)</f>
+        <f>IF(J11&gt;5000,100*I13,50*I13)</f>
         <v>0</v>
       </c>
       <c r="J17" s="86" t="str">
@@ -3710,7 +3713,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="B18" s="74" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" s="81" t="str">
         <f>C15+C17</f>
@@ -3747,7 +3750,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="79" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="81" t="str">
         <f>C16+C17</f>
@@ -3784,7 +3787,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="75" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
@@ -3792,7 +3795,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="74" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" s="81">
         <v>0</v>
@@ -3825,13 +3828,13 @@
         <v>0</v>
       </c>
       <c r="D27" s="87">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="E27" s="87">
         <v>0</v>
       </c>
       <c r="F27" s="87">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G27" s="87">
         <v>0</v>
@@ -3849,7 +3852,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="B28" s="74" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="81" t="str">
         <f>MAX(C19,C18)*C27</f>
@@ -3886,7 +3889,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="B29" s="74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="81" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
@@ -3923,7 +3926,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="81" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
@@ -3960,7 +3963,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" s="81" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
@@ -3997,7 +4000,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="81" t="str">
         <f>SUM(C28:C31)</f>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="37" spans="1:14">
       <c r="B37" s="75" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
@@ -4042,7 +4045,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="B40" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C40" s="81" t="str">
         <f>C13*J40</f>
@@ -4082,36 +4085,36 @@
     </row>
     <row r="43" spans="1:14">
       <c r="B43" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C43" s="74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J43" s="74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="B44" s="74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C44" s="81" t="str">
         <f>SUM(C15,C40,C32,(C26))</f>
@@ -4148,34 +4151,34 @@
     </row>
     <row r="45" spans="1:14">
       <c r="B45" s="74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="74">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D45" s="74">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="E45" s="74">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F45" s="74">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="G45" s="74">
-        <v>200</v>
+        <v>460</v>
       </c>
       <c r="H45" s="74">
-        <v>525</v>
+        <v>51</v>
       </c>
       <c r="I45" s="74">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="J45" s="74"/>
     </row>
     <row r="46" spans="1:14">
       <c r="B46" s="74" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C46" s="81" t="str">
         <f>SUM(C44/C45)</f>
@@ -4209,7 +4212,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="B47" s="74" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C47" s="85" t="str">
         <f>C46*3.7</f>
